--- a/data/trans_orig/P36B17-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B17-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>176217</t>
+          <t>197666</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>158559</t>
+          <t>177841</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>196006</t>
+          <t>219480</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>341004</t>
+          <t>367752</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>320230</t>
+          <t>344413</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>362052</t>
+          <t>390186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>517221</t>
+          <t>565418</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>489651</t>
+          <t>533606</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>549572</t>
+          <t>595507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>152254</t>
+          <t>178438</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132227</t>
+          <t>156517</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172228</t>
+          <t>199898</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>205788</t>
+          <t>224435</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>188194</t>
+          <t>205048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224438</t>
+          <t>243441</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>358042</t>
+          <t>402873</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>331685</t>
+          <t>374310</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>386250</t>
+          <t>435371</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>137025</t>
+          <t>147598</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117564</t>
+          <t>129181</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159276</t>
+          <t>169201</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>167091</t>
+          <t>185108</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>148947</t>
+          <t>168185</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>185890</t>
+          <t>206675</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>304116</t>
+          <t>332706</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>275051</t>
+          <t>305426</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>336218</t>
+          <t>361619</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30337</t>
+          <t>33565</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21681</t>
+          <t>23596</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43628</t>
+          <t>46892</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33580</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25041</t>
+          <t>27151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46759</t>
+          <t>48559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>63917</t>
+          <t>69716</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51680</t>
+          <t>55690</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81253</t>
+          <t>87756</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>19322</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26642</t>
+          <t>30032</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,27 +1212,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1247,27 +1247,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>25118</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>17348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32475</t>
+          <t>35860</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>513018</t>
+          <t>576590</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>513018</t>
+          <t>576590</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>513018</t>
+          <t>576590</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>752682</t>
+          <t>819241</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>752682</t>
+          <t>819241</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>752682</t>
+          <t>819241</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1265700</t>
+          <t>1395831</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1265700</t>
+          <t>1395831</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1265700</t>
+          <t>1395831</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>443970</t>
+          <t>493878</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>292367</t>
+          <t>453581</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>516757</t>
+          <t>540451</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>651539</t>
+          <t>513830</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>472775</t>
+          <t>480237</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1134531</t>
+          <t>546174</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1095509</t>
+          <t>1007708</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>867966</t>
+          <t>952582</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1609444</t>
+          <t>1062418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>627015</t>
+          <t>684953</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>439622</t>
+          <t>636076</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>720716</t>
+          <t>732877</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>719692</t>
+          <t>802020</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>531272</t>
+          <t>764335</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>815794</t>
+          <t>847639</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1346707</t>
+          <t>1486972</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1087215</t>
+          <t>1417350</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1503072</t>
+          <t>1550011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>751563</t>
+          <t>808432</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>512976</t>
+          <t>755154</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>862927</t>
+          <t>860073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>723070</t>
+          <t>689918</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>536199</t>
+          <t>648936</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>866537</t>
+          <t>733432</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1474633</t>
+          <t>1498350</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1179965</t>
+          <t>1433740</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1655092</t>
+          <t>1566762</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>169014</t>
+          <t>179692</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118017</t>
+          <t>148485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>207753</t>
+          <t>216904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>104460</t>
+          <t>117898</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71804</t>
+          <t>97094</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127432</t>
+          <t>140898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>273473</t>
+          <t>297590</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>221654</t>
+          <t>263944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330162</t>
+          <t>336584</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>297134</t>
+          <t>62026</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53034</t>
+          <t>45109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>969630</t>
+          <t>81674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33848</t>
+          <t>40571</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21567</t>
+          <t>28522</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47491</t>
+          <t>54888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>330982</t>
+          <t>102597</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82241</t>
+          <t>81091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1091351</t>
+          <t>127904</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2288697</t>
+          <t>2228980</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2288697</t>
+          <t>2228980</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2288697</t>
+          <t>2228980</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2232608</t>
+          <t>2164237</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2232608</t>
+          <t>2164237</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2232608</t>
+          <t>2164237</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4521305</t>
+          <t>4393217</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4521305</t>
+          <t>4393217</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4521305</t>
+          <t>4393217</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>195345</t>
+          <t>218381</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>171839</t>
+          <t>191707</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>221025</t>
+          <t>246588</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>186654</t>
+          <t>216282</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>167527</t>
+          <t>193713</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207082</t>
+          <t>237159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>381998</t>
+          <t>434663</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>352031</t>
+          <t>404052</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>414903</t>
+          <t>469570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>237018</t>
+          <t>263278</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>212477</t>
+          <t>235763</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>265946</t>
+          <t>291928</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>275573</t>
+          <t>303017</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>252316</t>
+          <t>279139</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>296716</t>
+          <t>329203</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>512591</t>
+          <t>566295</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>478598</t>
+          <t>531409</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>548274</t>
+          <t>603769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>180160</t>
+          <t>191774</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155882</t>
+          <t>169655</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>214296</t>
+          <t>222826</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>172113</t>
+          <t>186707</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>151927</t>
+          <t>166460</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>193173</t>
+          <t>209396</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>352274</t>
+          <t>378482</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>319215</t>
+          <t>344338</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>390628</t>
+          <t>414643</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27292</t>
+          <t>30620</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18320</t>
+          <t>20387</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39816</t>
+          <t>45211</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21811</t>
+          <t>24320</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14028</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32578</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>49103</t>
+          <t>54940</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37309</t>
+          <t>41753</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65495</t>
+          <t>73830</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8632</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>645789</t>
+          <t>710742</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>645789</t>
+          <t>710742</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>645789</t>
+          <t>710742</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1306252</t>
+          <t>1445619</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1306252</t>
+          <t>1445619</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1306252</t>
+          <t>1445619</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>815532</t>
+          <t>909925</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>628661</t>
+          <t>858314</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>894779</t>
+          <t>964446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1179196</t>
+          <t>1097863</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1009290</t>
+          <t>1053463</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1608420</t>
+          <t>1147821</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1994728</t>
+          <t>2007789</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1766117</t>
+          <t>1932257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2540265</t>
+          <t>2076028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1016288</t>
+          <t>1126669</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>777211</t>
+          <t>1067697</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1111935</t>
+          <t>1185826</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1201053</t>
+          <t>1329471</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>979206</t>
+          <t>1276821</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1299578</t>
+          <t>1377816</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2217341</t>
+          <t>2456140</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1906165</t>
+          <t>2384070</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2372207</t>
+          <t>2533520</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1068748</t>
+          <t>1147804</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>810007</t>
+          <t>1083125</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1172575</t>
+          <t>1211771</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1062274</t>
+          <t>1061734</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>900896</t>
+          <t>1012303</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1215764</t>
+          <t>1113874</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2131023</t>
+          <t>2209537</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1852532</t>
+          <t>2117907</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2316880</t>
+          <t>2283157</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>226642</t>
+          <t>243877</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>174377</t>
+          <t>206224</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>269877</t>
+          <t>281043</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>159851</t>
+          <t>178369</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>127396</t>
+          <t>154087</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>188296</t>
+          <t>204873</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>386493</t>
+          <t>422246</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>332899</t>
+          <t>381885</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>440514</t>
+          <t>477319</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>320293</t>
+          <t>88037</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76134</t>
+          <t>69282</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1109653</t>
+          <t>111981</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>43380</t>
+          <t>50918</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>31992</t>
+          <t>37211</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59412</t>
+          <t>65222</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>363673</t>
+          <t>138954</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>114221</t>
+          <t>114946</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1323703</t>
+          <t>170245</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3447504</t>
+          <t>3516312</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3447504</t>
+          <t>3516312</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3447504</t>
+          <t>3516312</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3645753</t>
+          <t>3718355</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3645753</t>
+          <t>3718355</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3645753</t>
+          <t>3718355</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7093257</t>
+          <t>7234667</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7093257</t>
+          <t>7234667</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7093257</t>
+          <t>7234667</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
